--- a/Switch Functions/GaN Data Check.xlsx
+++ b/Switch Functions/GaN Data Check.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MIT\Project\GE Vernova\Github\Switch Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592FFCD8-A17B-42EA-8FD6-FAC5876F80E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F34BAEF9-09BE-4FB7-B43C-B6C5006CDBA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>Part Number</t>
   </si>
@@ -138,12 +138,6 @@
   </si>
   <si>
     <t>Infineon IGLT65R035</t>
-  </si>
-  <si>
-    <t>IGOT65R035D2AUMA1</t>
-  </si>
-  <si>
-    <t>Infineon IGOT65R035</t>
   </si>
   <si>
     <t>Infineon IGOT65R025</t>
@@ -574,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X7"/>
+  <dimension ref="A1:X6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" customWidth="1"/>
@@ -707,7 +701,7 @@
         <v>6.3</v>
       </c>
       <c r="M2" s="7">
-        <f t="shared" ref="M2:M7" si="0">R2/X2</f>
+        <f t="shared" ref="M2:M6" si="0">R2/X2</f>
         <v>1.571428571428571</v>
       </c>
       <c r="N2" s="2">
@@ -723,7 +717,7 @@
         <v>1.9</v>
       </c>
       <c r="R2" s="2">
-        <f t="shared" ref="R2:R7" si="1">Q2-P2</f>
+        <f t="shared" ref="R2:R6" si="1">Q2-P2</f>
         <v>0.99999999999999989</v>
       </c>
       <c r="S2" s="2">
@@ -733,7 +727,7 @@
         <v>1.7</v>
       </c>
       <c r="U2" s="2">
-        <f t="shared" ref="U2:U7" si="2">V2+W2</f>
+        <f t="shared" ref="U2:U6" si="2">V2+W2</f>
         <v>3.3</v>
       </c>
       <c r="V2" s="2">
@@ -743,7 +737,7 @@
         <v>2</v>
       </c>
       <c r="X2" s="2">
-        <f t="shared" ref="X2:X7" si="3">(S2+T2)/(2*U2)</f>
+        <f t="shared" ref="X2:X6" si="3">(S2+T2)/(2*U2)</f>
         <v>0.63636363636363646</v>
       </c>
     </row>
@@ -980,22 +974,22 @@
     </row>
     <row r="6" spans="1:24" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>35</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>34</v>
       </c>
       <c r="C6" s="4">
         <v>650</v>
       </c>
       <c r="D6" s="4">
-        <v>0.94</v>
+        <v>0.68</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G6" s="4">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="H6" s="4">
         <v>15.64</v>
@@ -1004,33 +998,33 @@
         <v>10.85</v>
       </c>
       <c r="J6" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="K6" s="2">
         <v>150</v>
       </c>
       <c r="L6" s="7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M6" s="7">
         <f t="shared" si="0"/>
-        <v>1.8267333333333329</v>
+        <v>1.5466666666666671</v>
       </c>
       <c r="N6" s="2">
-        <v>7.7</v>
+        <v>11</v>
       </c>
       <c r="O6" s="2">
         <v>3</v>
       </c>
       <c r="P6" s="2">
-        <v>0.66700000000000004</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="R6" s="2">
         <f t="shared" si="1"/>
-        <v>0.58299999999999996</v>
+        <v>0.8</v>
       </c>
       <c r="S6" s="2">
         <v>1.8</v>
@@ -1040,90 +1034,15 @@
       </c>
       <c r="U6" s="2">
         <f t="shared" si="2"/>
-        <v>4.6999999999999993</v>
+        <v>2.9000000000000004</v>
       </c>
       <c r="V6" s="2">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="W6" s="2">
-        <v>3.3</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="X6" s="2">
-        <f t="shared" si="3"/>
-        <v>0.31914893617021284</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="4">
-        <v>650</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.68</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="4">
-        <v>130</v>
-      </c>
-      <c r="H7" s="4">
-        <v>15.64</v>
-      </c>
-      <c r="I7" s="4">
-        <v>10.85</v>
-      </c>
-      <c r="J7" s="2">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="K7" s="2">
-        <v>150</v>
-      </c>
-      <c r="L7" s="7">
-        <v>12</v>
-      </c>
-      <c r="M7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.5466666666666671</v>
-      </c>
-      <c r="N7" s="2">
-        <v>11</v>
-      </c>
-      <c r="O7" s="2">
-        <v>3</v>
-      </c>
-      <c r="P7" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>1.8</v>
-      </c>
-      <c r="R7" s="2">
-        <f t="shared" si="1"/>
-        <v>0.8</v>
-      </c>
-      <c r="S7" s="2">
-        <v>1.8</v>
-      </c>
-      <c r="T7" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="U7" s="2">
-        <f t="shared" si="2"/>
-        <v>2.9000000000000004</v>
-      </c>
-      <c r="V7" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="W7" s="2">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="X7" s="2">
         <f t="shared" si="3"/>
         <v>0.51724137931034475</v>
       </c>
@@ -1137,8 +1056,7 @@
     <hyperlink ref="B4" r:id="rId2" xr:uid="{D721005D-7D84-4B1B-8977-DD5060454D9B}"/>
     <hyperlink ref="B2" r:id="rId3" xr:uid="{A3A31E43-474D-4BD8-8613-CDDAF7E623D3}"/>
     <hyperlink ref="B5" r:id="rId4" xr:uid="{B485EA92-93D0-4B32-844A-296EC4364521}"/>
-    <hyperlink ref="B6" r:id="rId5" xr:uid="{D8D21754-68AE-4A96-85D5-E765578A6996}"/>
-    <hyperlink ref="B7" r:id="rId6" xr:uid="{0D96658A-923E-4FCF-920F-D72B38E2D00A}"/>
+    <hyperlink ref="B6" r:id="rId5" xr:uid="{0D96658A-923E-4FCF-920F-D72B38E2D00A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
